--- a/debug/judgements_q_sty_swi/excel_overviews/overview_simple.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/overview_simple.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="223">
   <si>
     <t>vs_Llama-2-7b-chat-hf</t>
   </si>
@@ -40,12 +40,21 @@
     <t>vs_gemini-1.5-flash</t>
   </si>
   <si>
+    <t>vs_gpt-4.1_errors</t>
+  </si>
+  <si>
     <t>Judge Model</t>
   </si>
   <si>
+    <t>Llama-3.1-8B-Instruct</t>
+  </si>
+  <si>
     <t>Qwen3-4B-Instruct-2507</t>
   </si>
   <si>
+    <t>Mistral-Small-3.2-24B-Instruct-2506</t>
+  </si>
+  <si>
     <t>Mistral-7B-Instruct-v0.3</t>
   </si>
   <si>
@@ -58,8 +67,16 @@
     <t>Llama-3.3-70B-Instruct</t>
   </si>
   <si>
-    <t>ASR: 0.21
-V1: 127 V2: 5 Vties: 10</t>
+    <t>ASR: 0.32
+V1: 117 V2: 11 Vties: 13</t>
+  </si>
+  <si>
+    <t>ASR: 0.22
+V1: 129 V2: 5 Vties: 8</t>
+  </si>
+  <si>
+    <t>ASR: 0.08
+V1: 133 V2: 5 Vties: 4</t>
   </si>
   <si>
     <t>ASR: 0.40
@@ -78,8 +95,16 @@
 V1: 126 V2: 7 Vties: 9</t>
   </si>
   <si>
-    <t>ASR: 0.52
-V1: 89 V2: 33 Vties: 20</t>
+    <t>ASR: 0.60
+V1: 81 V2: 38 Vties: 23</t>
+  </si>
+  <si>
+    <t>ASR: 0.54
+V1: 89 V2: 35 Vties: 18</t>
+  </si>
+  <si>
+    <t>ASR: 0.31
+V1: 83 V2: 42 Vties: 17</t>
   </si>
   <si>
     <t>ASR: 0.45
@@ -98,8 +123,16 @@
 V1: 45 V2: 59 Vties: 38</t>
   </si>
   <si>
-    <t>ASR: 0.43
-V1: 93 V2: 27 Vties: 22</t>
+    <t>ASR: 0.53
+V1: 81 V2: 36 Vties: 24</t>
+  </si>
+  <si>
+    <t>ASR: 0.46
+V1: 93 V2: 29 Vties: 20</t>
+  </si>
+  <si>
+    <t>ASR: 0.32
+V1: 95 V2: 27 Vties: 20</t>
   </si>
   <si>
     <t>ASR: 0.56
@@ -118,8 +151,16 @@
 V1: 75 V2: 36 Vties: 31</t>
   </si>
   <si>
-    <t>ASR: 0.08
+    <t>ASR: 0.17
+V1: 121 V2: 9 Vties: 8</t>
+  </si>
+  <si>
+    <t>ASR: 0.07
 V1: 136 V2: 3 Vties: 3</t>
+  </si>
+  <si>
+    <t>ASR: 0.01
+V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
     <t>ASR: 0.23
@@ -138,8 +179,16 @@
 V1: 132 V2: 3 Vties: 7</t>
   </si>
   <si>
-    <t>ASR: 0.45
-V1: 62 V2: 65 Vties: 15</t>
+    <t>ASR: 0.49
+V1: 37 V2: 77 Vties: 27</t>
+  </si>
+  <si>
+    <t>ASR: 0.41
+V1: 61 V2: 68 Vties: 13</t>
+  </si>
+  <si>
+    <t>ASR: 0.41
+V1: 61 V2: 69 Vties: 12</t>
   </si>
   <si>
     <t>ASR: 0.51
@@ -158,8 +207,16 @@
 V1: 31 V2: 78 Vties: 33</t>
   </si>
   <si>
-    <t>ASR: 0.25
+    <t>ASR: 0.34
+V1: 101 V2: 21 Vties: 17</t>
+  </si>
+  <si>
+    <t>ASR: 0.26
 V1: 117 V2: 13 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR: 0.16
+V1: 123 V2: 15 Vties: 4</t>
   </si>
   <si>
     <t>ASR: 0.36
@@ -178,8 +235,16 @@
 V1: 115 V2: 12 Vties: 15</t>
   </si>
   <si>
-    <t>ASR: 0.69
-V1: 87 V2: 36 Vties: 19</t>
+    <t>ASR: 0.59
+V1: 49 V2: 57 Vties: 34</t>
+  </si>
+  <si>
+    <t>ASR: 0.68
+V1: 82 V2: 35 Vties: 25</t>
+  </si>
+  <si>
+    <t>ASR: 0.36
+V1: 92 V2: 28 Vties: 22</t>
   </si>
   <si>
     <t>ASR: 0.54
@@ -198,8 +263,28 @@
 V1: 79 V2: 34 Vties: 29</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 127 V2: 5 Vties: 10</t>
+    <t>ASR: 0.56
+V1: 113 V2: 9 Vties: 15</t>
+  </si>
+  <si>
+    <t>ASR: 0.41
+V1: 103 V2: 0 Vties: 39</t>
+  </si>
+  <si>
+    <t>ASR: 0.36
+V1: 130 V2: 5 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR: 0.09
+V1: 117 V2: 11 Vties: 13</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 129 V2: 5 Vties: 8</t>
+  </si>
+  <si>
+    <t>AASR: 0.20
+V1: 133 V2: 5 Vties: 4</t>
   </si>
   <si>
     <t>AASR: 0.07
@@ -218,8 +303,16 @@
 V1: 126 V2: 7 Vties: 9</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 89 V2: 33 Vties: 20</t>
+    <t>AASR: 0.05
+V1: 81 V2: 38 Vties: 23</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 89 V2: 35 Vties: 18</t>
+  </si>
+  <si>
+    <t>AASR: 0.12
+V1: 83 V2: 42 Vties: 17</t>
   </si>
   <si>
     <t>AASR: 0.10
@@ -239,7 +332,11 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 93 V2: 27 Vties: 22</t>
+V1: 81 V2: 36 Vties: 24</t>
+  </si>
+  <si>
+    <t>AASR: 0.11
+V1: 95 V2: 27 Vties: 20</t>
   </si>
   <si>
     <t>AASR: 0.03
@@ -258,8 +355,16 @@
 V1: 75 V2: 36 Vties: 31</t>
   </si>
   <si>
+    <t>AASR: 0.22
+V1: 121 V2: 9 Vties: 8</t>
+  </si>
+  <si>
     <t>AASR: 0.00
 V1: 136 V2: 3 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR: 1.00
+V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
     <t>AASR: 0.25
@@ -278,8 +383,16 @@
 V1: 132 V2: 3 Vties: 7</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 62 V2: 65 Vties: 15</t>
+    <t>AASR: 0.04
+V1: 37 V2: 77 Vties: 27</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 61 V2: 68 Vties: 13</t>
+  </si>
+  <si>
+    <t>AASR: 0.06
+V1: 61 V2: 69 Vties: 12</t>
   </si>
   <si>
     <t>AASR: 0.05
@@ -298,8 +411,16 @@
 V1: 31 V2: 78 Vties: 33</t>
   </si>
   <si>
+    <t>AASR: 0.10
+V1: 101 V2: 21 Vties: 17</t>
+  </si>
+  <si>
     <t>AASR: 0.00
 V1: 117 V2: 13 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR: 0.33
+V1: 123 V2: 15 Vties: 4</t>
   </si>
   <si>
     <t>AASR: 0.29
@@ -318,8 +439,16 @@
 V1: 115 V2: 12 Vties: 15</t>
   </si>
   <si>
-    <t>AASR: 0.03
-V1: 87 V2: 36 Vties: 19</t>
+    <t>AASR: 0.04
+V1: 49 V2: 57 Vties: 34</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 82 V2: 35 Vties: 25</t>
+  </si>
+  <si>
+    <t>AASR: 0.14
+V1: 92 V2: 28 Vties: 22</t>
   </si>
   <si>
     <t>AASR: 0.00
@@ -338,8 +467,28 @@
 V1: 79 V2: 34 Vties: 29</t>
   </si>
   <si>
+    <t>AASR: 0.00
+V1: 113 V2: 9 Vties: 15</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 103 V2: 0 Vties: 39</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 130 V2: 5 Vties: 7</t>
+  </si>
+  <si>
+    <t>FR: 0.37
+V1: 117 V2: 11 Vties: 13</t>
+  </si>
+  <si>
     <t>FR: 0.26
-V1: 127 V2: 5 Vties: 10</t>
+V1: 129 V2: 5 Vties: 8</t>
+  </si>
+  <si>
+    <t>FR: 0.11
+V1: 133 V2: 5 Vties: 4</t>
   </si>
   <si>
     <t>FR: 0.48
@@ -358,8 +507,16 @@
 V1: 126 V2: 7 Vties: 9</t>
   </si>
   <si>
+    <t>FR: 0.52
+V1: 81 V2: 38 Vties: 23</t>
+  </si>
+  <si>
     <t>FR: 0.46
-V1: 89 V2: 33 Vties: 20</t>
+V1: 89 V2: 35 Vties: 18</t>
+  </si>
+  <si>
+    <t>FR: 0.34
+V1: 83 V2: 42 Vties: 17</t>
   </si>
   <si>
     <t>FR: 0.54
@@ -378,8 +535,16 @@
 V1: 45 V2: 59 Vties: 38</t>
   </si>
   <si>
+    <t>FR: 0.48
+V1: 81 V2: 36 Vties: 24</t>
+  </si>
+  <si>
     <t>FR: 0.44
-V1: 93 V2: 27 Vties: 22</t>
+V1: 93 V2: 29 Vties: 20</t>
+  </si>
+  <si>
+    <t>FR: 0.37
+V1: 95 V2: 27 Vties: 20</t>
   </si>
   <si>
     <t>FR: 0.56
@@ -398,8 +563,16 @@
 V1: 75 V2: 36 Vties: 31</t>
   </si>
   <si>
-    <t>FR: 0.10
+    <t>FR: 0.22
+V1: 121 V2: 9 Vties: 8</t>
+  </si>
+  <si>
+    <t>FR: 0.09
 V1: 136 V2: 3 Vties: 3</t>
+  </si>
+  <si>
+    <t>FR: 0.04
+V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
     <t>FR: 0.31
@@ -418,8 +591,16 @@
 V1: 132 V2: 3 Vties: 7</t>
   </si>
   <si>
-    <t>FR: 0.30
-V1: 62 V2: 65 Vties: 15</t>
+    <t>FR: 0.34
+V1: 37 V2: 77 Vties: 27</t>
+  </si>
+  <si>
+    <t>FR: 0.27
+V1: 61 V2: 68 Vties: 13</t>
+  </si>
+  <si>
+    <t>FR: 0.29
+V1: 61 V2: 69 Vties: 12</t>
   </si>
   <si>
     <t>FR: 0.56
@@ -438,8 +619,16 @@
 V1: 31 V2: 78 Vties: 33</t>
   </si>
   <si>
-    <t>FR: 0.29
+    <t>FR: 0.38
+V1: 101 V2: 21 Vties: 17</t>
+  </si>
+  <si>
+    <t>FR: 0.30
 V1: 117 V2: 13 Vties: 12</t>
+  </si>
+  <si>
+    <t>FR: 0.20
+V1: 123 V2: 15 Vties: 4</t>
   </si>
   <si>
     <t>FR: 0.50
@@ -458,8 +647,16 @@
 V1: 115 V2: 12 Vties: 15</t>
   </si>
   <si>
-    <t>FR: 0.56
-V1: 87 V2: 36 Vties: 19</t>
+    <t>FR: 0.46
+V1: 49 V2: 57 Vties: 34</t>
+  </si>
+  <si>
+    <t>FR: 0.57
+V1: 82 V2: 35 Vties: 25</t>
+  </si>
+  <si>
+    <t>FR: 0.42
+V1: 92 V2: 28 Vties: 22</t>
   </si>
   <si>
     <t>FR: 0.75
@@ -478,8 +675,28 @@
 V1: 79 V2: 34 Vties: 29</t>
   </si>
   <si>
-    <t>CR: 0.80
-V1: 127 V2: 5 Vties: 10</t>
+    <t>FR: 0.57
+V1: 113 V2: 9 Vties: 15</t>
+  </si>
+  <si>
+    <t>FR: 0.57
+V1: 103 V2: 0 Vties: 39</t>
+  </si>
+  <si>
+    <t>FR: 0.38
+V1: 130 V2: 5 Vties: 7</t>
+  </si>
+  <si>
+    <t>CR: 0.70
+V1: 117 V2: 11 Vties: 13</t>
+  </si>
+  <si>
+    <t>CR: 0.78
+V1: 129 V2: 5 Vties: 8</t>
+  </si>
+  <si>
+    <t>CR: 0.91
+V1: 133 V2: 5 Vties: 4</t>
   </si>
   <si>
     <t>CR: 0.64
@@ -498,8 +715,16 @@
 V1: 126 V2: 7 Vties: 9</t>
   </si>
   <si>
-    <t>CR: 0.62
-V1: 89 V2: 33 Vties: 20</t>
+    <t>CR: 0.57
+V1: 81 V2: 38 Vties: 23</t>
+  </si>
+  <si>
+    <t>CR: 0.61
+V1: 89 V2: 35 Vties: 18</t>
+  </si>
+  <si>
+    <t>CR: 0.75
+V1: 83 V2: 42 Vties: 17</t>
   </si>
   <si>
     <t>CR: 0.65
@@ -518,8 +743,16 @@
 V1: 45 V2: 59 Vties: 38</t>
   </si>
   <si>
-    <t>CR: 0.67
-V1: 93 V2: 27 Vties: 22</t>
+    <t>CR: 0.63
+V1: 81 V2: 36 Vties: 24</t>
+  </si>
+  <si>
+    <t>CR: 0.65
+V1: 93 V2: 29 Vties: 20</t>
+  </si>
+  <si>
+    <t>CR: 0.73
+V1: 95 V2: 27 Vties: 20</t>
   </si>
   <si>
     <t>CR: 0.62
@@ -538,8 +771,16 @@
 V1: 75 V2: 36 Vties: 31</t>
   </si>
   <si>
-    <t>CR: 0.92
+    <t>CR: 0.83
+V1: 121 V2: 9 Vties: 8</t>
+  </si>
+  <si>
+    <t>CR: 0.93
 V1: 136 V2: 3 Vties: 3</t>
+  </si>
+  <si>
+    <t>CR: 0.98
+V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
     <t>CR: 0.77
@@ -558,8 +799,16 @@
 V1: 132 V2: 3 Vties: 7</t>
   </si>
   <si>
+    <t>CR: 0.82
+V1: 37 V2: 77 Vties: 27</t>
+  </si>
+  <si>
+    <t>CR: 0.81
+V1: 61 V2: 68 Vties: 13</t>
+  </si>
+  <si>
     <t>CR: 0.78
-V1: 62 V2: 65 Vties: 15</t>
+V1: 61 V2: 69 Vties: 12</t>
   </si>
   <si>
     <t>CR: 0.73
@@ -578,8 +827,16 @@
 V1: 31 V2: 78 Vties: 33</t>
   </si>
   <si>
-    <t>CR: 0.78
+    <t>CR: 0.70
+V1: 101 V2: 21 Vties: 17</t>
+  </si>
+  <si>
+    <t>CR: 0.77
 V1: 117 V2: 13 Vties: 12</t>
+  </si>
+  <si>
+    <t>CR: 0.82
+V1: 123 V2: 15 Vties: 4</t>
   </si>
   <si>
     <t>CR: 0.65
@@ -598,8 +855,16 @@
 V1: 115 V2: 12 Vties: 15</t>
   </si>
   <si>
-    <t>CR: 0.50
-V1: 87 V2: 36 Vties: 19</t>
+    <t>CR: 0.71
+V1: 49 V2: 57 Vties: 34</t>
+  </si>
+  <si>
+    <t>CR: 0.52
+V1: 82 V2: 35 Vties: 25</t>
+  </si>
+  <si>
+    <t>CR: 0.69
+V1: 92 V2: 28 Vties: 22</t>
   </si>
   <si>
     <t>CR: 0.62
@@ -616,6 +881,18 @@
   <si>
     <t>CR: 0.73
 V1: 79 V2: 34 Vties: 29</t>
+  </si>
+  <si>
+    <t>CR: 0.48
+V1: 113 V2: 9 Vties: 15</t>
+  </si>
+  <si>
+    <t>CR: 0.59
+V1: 103 V2: 0 Vties: 39</t>
+  </si>
+  <si>
+    <t>CR: 0.65
+V1: 130 V2: 5 Vties: 7</t>
   </si>
 </sst>
 </file>
@@ -976,15 +1253,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="9" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="10" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1007,135 +1284,199 @@
       <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>47</v>
+      <c r="F8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1145,15 +1486,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="9" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="10" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1176,135 +1517,199 @@
       <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>82</v>
+      <c r="D8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1314,15 +1719,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="9" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="10" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1345,135 +1750,199 @@
       <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>161</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>162</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>163</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>117</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -1483,15 +1952,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="9" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="10" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1514,135 +1983,199 @@
       <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>123</v>
+        <v>178</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>213</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>139</v>
+        <v>200</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>214</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>135</v>
+        <v>194</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>215</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>146</v>
+        <v>209</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>147</v>
+        <v>210</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>152</v>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
